--- a/data/raw/padi/table2.xlsx
+++ b/data/raw/padi/table2.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\01_Life\Business\Penlogik\marketing\30day_chart_challenge\2026\30dayChartChallenge\data\raw\padi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25B203A7-BB25-40C7-A824-AF449388C356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D487C912-5592-4E3A-A5DF-EEA8F6C5A138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{D2F845A1-056B-475D-A5F2-1C05D9208433}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D2F845A1-056B-475D-A5F2-1C05D9208433}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$1</definedName>
+  </definedNames>
   <calcPr calcId="181029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1025,24 +1028,24 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>154</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D4" t="s">
         <v>4</v>
@@ -1050,41 +1053,41 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>156</v>
+        <v>113</v>
       </c>
       <c r="D5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>157</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D7" t="s">
         <v>4</v>
@@ -1092,55 +1095,55 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>159</v>
+        <v>121</v>
       </c>
       <c r="D8" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>37</v>
+        <v>111</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="D9" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>161</v>
+        <v>119</v>
       </c>
       <c r="D10" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D11" t="s">
         <v>4</v>
@@ -1148,69 +1151,69 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>163</v>
+        <v>121</v>
       </c>
       <c r="D12" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>41</v>
+        <v>111</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>164</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>165</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="D15" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="D16" t="s">
         <v>4</v>
@@ -1218,83 +1221,83 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>168</v>
+        <v>121</v>
       </c>
       <c r="D17" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="D18" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="D19" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>171</v>
+        <v>135</v>
       </c>
       <c r="D20" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>172</v>
+        <v>106</v>
       </c>
       <c r="D21" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="D22" t="s">
         <v>4</v>
@@ -1302,83 +1305,83 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>174</v>
+        <v>128</v>
       </c>
       <c r="D23" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>52</v>
+        <v>121</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>175</v>
+        <v>122</v>
       </c>
       <c r="D24" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>53</v>
+        <v>112</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>176</v>
+        <v>56</v>
       </c>
       <c r="D25" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>177</v>
+        <v>57</v>
       </c>
       <c r="D26" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="D27" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="D28" t="s">
         <v>5</v>
@@ -1386,72 +1389,72 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>86</v>
+        <v>159</v>
       </c>
       <c r="D29" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="D30" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>58</v>
+        <v>128</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="D31" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D32" t="s">
         <v>9</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D32" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>60</v>
+        <v>113</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="D33" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -1459,38 +1462,38 @@
         <v>11</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>61</v>
+        <v>143</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="D34" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>179</v>
+        <v>99</v>
       </c>
       <c r="D35" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="D36" t="s">
         <v>5</v>
@@ -1498,125 +1501,125 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="D37" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>75</v>
+        <v>146</v>
       </c>
       <c r="D38" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>66</v>
+        <v>128</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>182</v>
+        <v>141</v>
       </c>
       <c r="D39" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>183</v>
+        <v>130</v>
       </c>
       <c r="D40" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>35</v>
+        <v>123</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>184</v>
+        <v>140</v>
       </c>
       <c r="D41" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>68</v>
+        <v>114</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>185</v>
+        <v>151</v>
       </c>
       <c r="D42" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>186</v>
+        <v>97</v>
       </c>
       <c r="D43" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>187</v>
+        <v>85</v>
       </c>
       <c r="D44" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="D45" t="s">
         <v>5</v>
@@ -1624,125 +1627,125 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>189</v>
+        <v>161</v>
       </c>
       <c r="D46" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>190</v>
+        <v>146</v>
       </c>
       <c r="D47" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>191</v>
+        <v>141</v>
       </c>
       <c r="D48" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>192</v>
+        <v>78</v>
       </c>
       <c r="D49" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>193</v>
+        <v>95</v>
       </c>
       <c r="D50" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>194</v>
+        <v>57</v>
       </c>
       <c r="D51" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>195</v>
+        <v>126</v>
       </c>
       <c r="D52" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>30</v>
+        <v>144</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="D53" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D54" t="s">
         <v>6</v>
@@ -1750,86 +1753,86 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="D55" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="D56" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="D57" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>99</v>
+        <v>147</v>
       </c>
       <c r="D58" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
+        <v>14</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D59" t="s">
         <v>12</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D59" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="D60" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
@@ -1837,66 +1840,66 @@
         <v>14</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="D61" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D62" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>89</v>
+        <v>149</v>
       </c>
       <c r="D63" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="D64" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D65" t="s">
         <v>6</v>
@@ -1904,282 +1907,282 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>91</v>
+        <v>181</v>
       </c>
       <c r="D66" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>36</v>
+        <v>163</v>
       </c>
       <c r="D67" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="D68" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="D69" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="D70" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>196</v>
+        <v>113</v>
       </c>
       <c r="D71" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>180</v>
+        <v>114</v>
       </c>
       <c r="D72" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>197</v>
+        <v>151</v>
       </c>
       <c r="D73" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>40</v>
+        <v>134</v>
       </c>
       <c r="D74" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>198</v>
+        <v>83</v>
       </c>
       <c r="D75" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="D76" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="D77" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="D78" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>131</v>
+        <v>164</v>
       </c>
       <c r="D79" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="D80" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>96</v>
+        <v>146</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="D81" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>97</v>
+        <v>147</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>144</v>
+        <v>112</v>
       </c>
       <c r="D82" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
+        <v>16</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D83" t="s">
         <v>13</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D83" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>60</v>
+        <v>142</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="D84" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="D85" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
@@ -2187,52 +2190,52 @@
         <v>16</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D86" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="D87" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="D88" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="D89" t="s">
         <v>7</v>
@@ -2240,181 +2243,181 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="D90" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>33</v>
+        <v>182</v>
       </c>
       <c r="D91" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>105</v>
+        <v>42</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>200</v>
+        <v>165</v>
       </c>
       <c r="D92" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>66</v>
+        <v>153</v>
       </c>
       <c r="D93" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>106</v>
+        <v>150</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>201</v>
+        <v>111</v>
       </c>
       <c r="D94" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="D95" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="D96" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D97" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="D98" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>93</v>
+        <v>152</v>
       </c>
       <c r="D99" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="D100" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
+        <v>17</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D101" t="s">
         <v>9</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D101" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="D102" t="s">
         <v>8</v>
@@ -2422,100 +2425,100 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>113</v>
+        <v>61</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="D103" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="D104" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>126</v>
+        <v>183</v>
       </c>
       <c r="D105" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="D106" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>83</v>
+        <v>153</v>
       </c>
       <c r="D107" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>59</v>
+        <v>150</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="D108" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="D109" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
@@ -2523,108 +2526,108 @@
         <v>18</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="D110" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>61</v>
+        <v>130</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D111" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="D112" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="D113" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="D114" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D115" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>119</v>
+        <v>31</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D116" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>34</v>
+        <v>138</v>
       </c>
       <c r="D117" t="s">
         <v>8</v>
@@ -2632,198 +2635,198 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D118" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>106</v>
       </c>
       <c r="D119" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>120</v>
+        <v>35</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>107</v>
+        <v>184</v>
       </c>
       <c r="D120" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>108</v>
+        <v>167</v>
       </c>
       <c r="D121" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>121</v>
+        <v>153</v>
       </c>
       <c r="D122" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B123" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C123" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C123" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="D123" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="D124" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>140</v>
+        <v>94</v>
       </c>
       <c r="D125" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="D126" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
+        <v>19</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D127" t="s">
         <v>14</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D127" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D128" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="D129" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D130" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>31</v>
+        <v>135</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="D131" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
@@ -2842,223 +2845,223 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>116</v>
+        <v>61</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D133" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="D134" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="D135" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>127</v>
+        <v>68</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>87</v>
+        <v>185</v>
       </c>
       <c r="D136" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>64</v>
+        <v>168</v>
       </c>
       <c r="D137" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>103</v>
+        <v>153</v>
       </c>
       <c r="D138" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>200</v>
+        <v>121</v>
       </c>
       <c r="D139" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>33</v>
+        <v>111</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>66</v>
+        <v>141</v>
       </c>
       <c r="D140" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>65</v>
+        <v>129</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>201</v>
+        <v>94</v>
       </c>
       <c r="D141" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>67</v>
+        <v>142</v>
       </c>
       <c r="D142" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>30</v>
+        <v>113</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>128</v>
+        <v>79</v>
       </c>
       <c r="D143" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D144" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>129</v>
+        <v>57</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="D145" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="D146" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>143</v>
+        <v>31</v>
       </c>
       <c r="D147" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>151</v>
+        <v>84</v>
       </c>
       <c r="D148" t="s">
         <v>10</v>
@@ -3066,58 +3069,58 @@
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="D149" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="D150" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>134</v>
+        <v>63</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="D151" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>135</v>
+        <v>88</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>145</v>
+        <v>36</v>
       </c>
       <c r="D152" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.3">
@@ -3125,178 +3128,178 @@
         <v>20</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>84</v>
+        <v>186</v>
       </c>
       <c r="D153" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>136</v>
+        <v>46</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>99</v>
+        <v>169</v>
       </c>
       <c r="D154" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="D155" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>61</v>
+        <v>150</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>62</v>
+        <v>121</v>
       </c>
       <c r="D156" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="D157" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>62</v>
+        <v>129</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>63</v>
+        <v>148</v>
       </c>
       <c r="D158" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="D159" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>63</v>
+        <v>142</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="D160" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>88</v>
+        <v>143</v>
       </c>
       <c r="D161" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>104</v>
+        <v>151</v>
       </c>
       <c r="D162" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>30</v>
+        <v>125</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="D163" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
+        <v>21</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D164" t="s">
         <v>12</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="D164" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>129</v>
+        <v>59</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="D165" t="s">
         <v>11</v>
@@ -3304,114 +3307,114 @@
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="D166" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="D167" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="D168" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>152</v>
+        <v>104</v>
       </c>
       <c r="D169" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="D170" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>149</v>
+        <v>187</v>
       </c>
       <c r="D171" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>31</v>
+        <v>170</v>
       </c>
       <c r="D172" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="D173" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.3">
@@ -3419,136 +3422,136 @@
         <v>22</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D174" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>60</v>
+        <v>121</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>99</v>
+        <v>147</v>
       </c>
       <c r="D175" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>202</v>
+        <v>112</v>
       </c>
       <c r="D176" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>61</v>
+        <v>148</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="D177" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="D178" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D179" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="D180" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>63</v>
+        <v>133</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="D181" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>146</v>
+        <v>97</v>
       </c>
       <c r="D182" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>141</v>
+        <v>98</v>
       </c>
       <c r="D183" t="s">
         <v>12</v>
@@ -3556,128 +3559,128 @@
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="D184" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="D185" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="D186" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D187" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>143</v>
+        <v>33</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>151</v>
+        <v>105</v>
       </c>
       <c r="D188" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>133</v>
+        <v>34</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="D189" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>134</v>
+        <v>188</v>
       </c>
       <c r="D190" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>144</v>
+        <v>48</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="D191" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>98</v>
+        <v>203</v>
       </c>
       <c r="D192" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.3">
@@ -3685,136 +3688,136 @@
         <v>23</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>31</v>
+        <v>153</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="D193" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="D194" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>60</v>
+        <v>141</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="D195" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>202</v>
+        <v>78</v>
       </c>
       <c r="D196" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>61</v>
+        <v>130</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="D197" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="D198" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="D199" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D200" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
+        <v>23</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D201" t="s">
         <v>14</v>
-      </c>
-      <c r="B201" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C201" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D201" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="D202" t="s">
         <v>13</v>
@@ -3822,100 +3825,100 @@
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>148</v>
+        <v>31</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="D203" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>123</v>
+        <v>60</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D204" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>132</v>
+        <v>62</v>
       </c>
       <c r="D205" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D206" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>57</v>
+        <v>118</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>152</v>
+        <v>65</v>
       </c>
       <c r="D207" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>126</v>
+        <v>67</v>
       </c>
       <c r="D208" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>97</v>
+        <v>179</v>
       </c>
       <c r="D209" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.3">
@@ -3923,178 +3926,178 @@
         <v>23</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>59</v>
+        <v>189</v>
       </c>
       <c r="D210" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>149</v>
+        <v>49</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>83</v>
+        <v>172</v>
       </c>
       <c r="D211" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>136</v>
+        <v>203</v>
       </c>
       <c r="D212" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D213" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>60</v>
+        <v>121</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="D214" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>202</v>
+        <v>122</v>
       </c>
       <c r="D215" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D216" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>150</v>
+        <v>113</v>
       </c>
       <c r="D217" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>146</v>
+        <v>56</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D218" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="D219" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="D220" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="D221" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>56</v>
+        <v>126</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="D222" t="s">
         <v>14</v>
@@ -4102,58 +4105,58 @@
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="D223" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="D224" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>81</v>
+        <v>202</v>
       </c>
       <c r="D225" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>96</v>
+        <v>138</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>144</v>
+        <v>86</v>
       </c>
       <c r="D226" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.3">
@@ -4161,223 +4164,223 @@
         <v>24</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>126</v>
+        <v>32</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="D227" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="D228" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>135</v>
+        <v>66</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="D229" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>136</v>
+        <v>196</v>
       </c>
       <c r="D230" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>116</v>
+        <v>190</v>
       </c>
       <c r="D231" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>99</v>
+        <v>173</v>
       </c>
       <c r="D232" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B233" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>150</v>
+        <v>203</v>
       </c>
       <c r="D233" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B234" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C234" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C234" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="D234" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B235" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C235" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C235" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="D235" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="D236" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="D237" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
+        <v>25</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D238" t="s">
         <v>20</v>
-      </c>
-      <c r="B238" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C238" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D238" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>143</v>
+        <v>95</v>
       </c>
       <c r="D239" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B240" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C240" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C240" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="D240" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>80</v>
+        <v>143</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="D241" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="D242" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.3">
@@ -4396,198 +4399,198 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>144</v>
+        <v>97</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>149</v>
+        <v>59</v>
       </c>
       <c r="D244" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>31</v>
+        <v>136</v>
       </c>
       <c r="D245" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>145</v>
+        <v>99</v>
       </c>
       <c r="D246" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="D247" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>150</v>
+        <v>63</v>
       </c>
       <c r="D248" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>150</v>
+        <v>87</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="D249" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>129</v>
+        <v>34</v>
       </c>
       <c r="D250" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>122</v>
+        <v>201</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="D251" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="D252" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>142</v>
+        <v>39</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>95</v>
+        <v>191</v>
       </c>
       <c r="D253" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>114</v>
+        <v>174</v>
       </c>
       <c r="D254" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>114</v>
+        <v>30</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>57</v>
+        <v>203</v>
       </c>
       <c r="D255" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>124</v>
+        <v>153</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D256" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="D257" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.3">
@@ -4595,94 +4598,94 @@
         <v>26</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D258" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>97</v>
+        <v>148</v>
       </c>
       <c r="D259" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="D260" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="D261" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>153</v>
+        <v>114</v>
       </c>
       <c r="D262" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
+        <v>26</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D263" t="s">
         <v>18</v>
-      </c>
-      <c r="B263" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C263" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D263" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="D264" t="s">
         <v>17</v>
@@ -4690,86 +4693,86 @@
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="D265" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>94</v>
+        <v>144</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="D266" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="D267" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="D268" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>143</v>
+        <v>202</v>
       </c>
       <c r="D269" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="D270" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.3">
@@ -4777,181 +4780,181 @@
         <v>26</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="D271" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>58</v>
+        <v>200</v>
       </c>
       <c r="D272" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>144</v>
+        <v>67</v>
       </c>
       <c r="D273" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>144</v>
+        <v>90</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="D274" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="D275" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>121</v>
+        <v>192</v>
       </c>
       <c r="D276" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>111</v>
+        <v>52</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>141</v>
+        <v>175</v>
       </c>
       <c r="D277" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>129</v>
+        <v>30</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>148</v>
+        <v>203</v>
       </c>
       <c r="D278" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="D279" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="D280" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
+        <v>27</v>
+      </c>
+      <c r="B281" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C281" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D281" t="s">
         <v>24</v>
-      </c>
-      <c r="B281" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C281" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D281" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>79</v>
+        <v>129</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="D282" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>132</v>
+        <v>94</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>57</v>
+        <v>130</v>
       </c>
       <c r="D283" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.3">
@@ -4959,153 +4962,153 @@
         <v>27</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>57</v>
+        <v>123</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>151</v>
+        <v>56</v>
       </c>
       <c r="D284" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>96</v>
+        <v>140</v>
       </c>
       <c r="D285" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D286" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D287" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="D288" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>141</v>
+        <v>97</v>
       </c>
       <c r="D289" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>112</v>
+        <v>31</v>
       </c>
       <c r="D290" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="D291" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="D292" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>113</v>
+        <v>61</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D293" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D294" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.3">
@@ -5113,153 +5116,153 @@
         <v>27</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>114</v>
+        <v>63</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D295" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>124</v>
+        <v>33</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>133</v>
+        <v>66</v>
       </c>
       <c r="D296" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="D297" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>153</v>
+        <v>69</v>
       </c>
       <c r="D298" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>150</v>
+        <v>93</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>121</v>
+        <v>40</v>
       </c>
       <c r="D299" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>121</v>
+        <v>74</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>147</v>
+        <v>193</v>
       </c>
       <c r="D300" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>141</v>
+        <v>53</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>122</v>
+        <v>176</v>
       </c>
       <c r="D301" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>112</v>
+        <v>30</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="D302" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D303" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
+        <v>28</v>
+      </c>
+      <c r="B304" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C304" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D304" t="s">
         <v>26</v>
-      </c>
-      <c r="B304" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C304" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="D304" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D305" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.3">
@@ -5267,52 +5270,52 @@
         <v>28</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="D306" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>57</v>
+        <v>130</v>
       </c>
       <c r="D307" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>30</v>
+        <v>123</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>153</v>
+        <v>113</v>
       </c>
       <c r="D308" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>150</v>
+        <v>56</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>128</v>
+        <v>79</v>
       </c>
       <c r="D309" t="s">
         <v>21</v>
@@ -5320,72 +5323,72 @@
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D310" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="D311" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D312" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="D313" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>56</v>
+        <v>135</v>
       </c>
       <c r="D314" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.3">
@@ -5393,111 +5396,111 @@
         <v>28</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="D315" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="D316" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>30</v>
+        <v>137</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>153</v>
+        <v>202</v>
       </c>
       <c r="D317" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="D318" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="D319" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>129</v>
+        <v>88</v>
       </c>
       <c r="D320" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>122</v>
+        <v>65</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>148</v>
+        <v>201</v>
       </c>
       <c r="D321" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="D322" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.3">
@@ -5505,111 +5508,111 @@
         <v>28</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D323" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>95</v>
+        <v>198</v>
       </c>
       <c r="D324" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="D325" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>153</v>
+        <v>54</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>128</v>
+        <v>177</v>
       </c>
       <c r="D326" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>128</v>
+        <v>30</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>77</v>
+        <v>203</v>
       </c>
       <c r="D327" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="D328" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
+        <v>29</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C329" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D329" t="s">
         <v>27</v>
-      </c>
-      <c r="B329" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C329" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D329" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="D330" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.3">
@@ -5617,24 +5620,24 @@
         <v>29</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="D331" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>30</v>
+        <v>148</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>203</v>
+        <v>78</v>
       </c>
       <c r="D332" t="s">
         <v>24</v>
@@ -5642,58 +5645,58 @@
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D333" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="D334" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="D335" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
       <c r="D336" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.3">
@@ -5701,69 +5704,69 @@
         <v>29</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>148</v>
+        <v>80</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>78</v>
+        <v>125</v>
       </c>
       <c r="D337" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>30</v>
+        <v>152</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>203</v>
+        <v>126</v>
       </c>
       <c r="D338" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>146</v>
+        <v>82</v>
       </c>
       <c r="D339" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="D340" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>141</v>
+        <v>60</v>
       </c>
       <c r="D341" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.3">
@@ -5771,55 +5774,55 @@
         <v>29</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="D342" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>203</v>
+        <v>85</v>
       </c>
       <c r="D343" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>153</v>
+        <v>62</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>146</v>
+        <v>117</v>
       </c>
       <c r="D344" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>128</v>
+        <v>63</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="D345" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.3">
@@ -5827,41 +5830,41 @@
         <v>29</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>141</v>
+        <v>104</v>
       </c>
       <c r="D346" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>203</v>
+        <v>67</v>
       </c>
       <c r="D347" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>153</v>
+        <v>90</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="D348" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.3">
@@ -5869,27 +5872,27 @@
         <v>29</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D349" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D350" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.3">
@@ -5897,13 +5900,13 @@
         <v>29</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="D351" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.3">
@@ -5911,16 +5914,21 @@
         <v>29</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>203</v>
+        <v>178</v>
       </c>
       <c r="D352" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D1" xr:uid="{62E25B7C-79AC-42BC-8960-BA38267B8AA6}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D352">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>